--- a/gte/nodes/P/compressor_stage_1_blade_rotor_coordinates_lattice.xlsx
+++ b/gte/nodes/P/compressor_stage_1_blade_rotor_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-22.388890849241182</v>
+        <v>4.9228764936436535</v>
       </c>
       <c r="B1">
-        <v>62.998921745496553</v>
+        <v>65.406955475237083</v>
       </c>
       <c r="C1">
         <v>338.08353538342624</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-15.1296102869794</v>
+        <v>9.8719177234146684</v>
       </c>
       <c r="B2">
-        <v>59.639003223759083</v>
+        <v>59.992741093231885</v>
       </c>
       <c r="C2">
         <v>338.08353538342624</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-10.711426172108286</v>
+        <v>12.223412770146664</v>
       </c>
       <c r="B3">
-        <v>56.218958053480151</v>
+        <v>55.470781706628181</v>
       </c>
       <c r="C3">
         <v>338.08353538342624</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-6.8844606908240769</v>
+        <v>14.091073897795589</v>
       </c>
       <c r="B4">
-        <v>52.7864008141282</v>
+        <v>51.115018876630643</v>
       </c>
       <c r="C4">
         <v>338.08353538342624</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-3.5051832942879941</v>
+        <v>15.59937507842346</v>
       </c>
       <c r="B5">
-        <v>49.344369069201989</v>
+        <v>46.882695895352811</v>
       </c>
       <c r="C5">
         <v>338.08353538342624</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-0.50680446981907468</v>
+        <v>16.802520105207481</v>
       </c>
       <c r="B6">
-        <v>45.894276297486748</v>
+        <v>42.755193804045106</v>
       </c>
       <c r="C6">
         <v>338.08353538342624</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>2.1524670299317985</v>
+        <v>17.733208031396114</v>
       </c>
       <c r="B7">
-        <v>42.437006934864179</v>
+        <v>38.721280504584946</v>
       </c>
       <c r="C7">
         <v>338.08353538342624</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>4.5012171284907954</v>
+        <v>18.41247575573394</v>
       </c>
       <c r="B8">
-        <v>38.973165950510435</v>
+        <v>34.773729839410585</v>
       </c>
       <c r="C8">
         <v>338.08353538342624</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>6.575062389334918</v>
+        <v>18.869507643181382</v>
       </c>
       <c r="B9">
-        <v>35.50350710433267</v>
+        <v>30.902517002959907</v>
       </c>
       <c r="C9">
         <v>338.08353538342624</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>8.4107110207044382</v>
+        <v>19.135108884614635</v>
       </c>
       <c r="B10">
-        <v>32.028807258917681</v>
+        <v>27.097060437290619</v>
       </c>
       <c r="C10">
         <v>338.08353538342624</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>10.042207169941895</v>
+        <v>19.238420508357162</v>
       </c>
       <c r="B11">
-        <v>28.549786896839734</v>
+        <v>23.347350222940076</v>
       </c>
       <c r="C11">
         <v>338.08353538342624</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>11.490114909340786</v>
+        <v>19.196193912073554</v>
       </c>
       <c r="B12">
-        <v>25.066881219356606</v>
+        <v>19.647632268472364</v>
       </c>
       <c r="C12">
         <v>338.08353538342624</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>12.723742071896227</v>
+        <v>18.977286133345576</v>
       </c>
       <c r="B13">
-        <v>21.57944068247264</v>
+        <v>16.008604156078995</v>
       </c>
       <c r="C13">
         <v>338.08353538342624</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>13.726127217337936</v>
+        <v>18.563799012673034</v>
       </c>
       <c r="B14">
-        <v>18.087106328096567</v>
+        <v>12.436413888951135</v>
       </c>
       <c r="C14">
         <v>338.08353538342624</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>14.58648805163257</v>
+        <v>18.0387079623106</v>
       </c>
       <c r="B15">
-        <v>14.591766287008053</v>
+        <v>8.9025594806512967</v>
       </c>
       <c r="C15">
         <v>338.08353538342624</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>15.386563829759158</v>
+        <v>17.478085107761462</v>
       </c>
       <c r="B16">
-        <v>11.095150422148109</v>
+        <v>5.3809102181110378</v>
       </c>
       <c r="C16">
         <v>338.08353538342624</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>16.072000856509455</v>
+        <v>16.829515855767852</v>
       </c>
       <c r="B17">
-        <v>7.5961084362321278</v>
+        <v>1.8894704713667849</v>
       </c>
       <c r="C17">
         <v>338.08353538342624</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>16.571530832670028</v>
+        <v>16.024747914684294</v>
       </c>
       <c r="B18">
-        <v>4.0931320650887608</v>
+        <v>-1.5483151530655321</v>
       </c>
       <c r="C18">
         <v>338.08353538342624</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>16.882319993193807</v>
+        <v>15.060664918075146</v>
       </c>
       <c r="B19">
-        <v>0.58616133722525532</v>
+        <v>-4.9313761858568705</v>
       </c>
       <c r="C19">
         <v>338.08353538342624</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>17.018643206575387</v>
+        <v>13.950434480807244</v>
       </c>
       <c r="B20">
-        <v>-2.92450164568152</v>
+        <v>-8.2642356919749318</v>
       </c>
       <c r="C20">
         <v>338.08353538342624</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>16.994775341309303</v>
+        <v>12.707224217747443</v>
       </c>
       <c r="B21">
-        <v>-6.4385547819546716</v>
+        <v>-11.551416736387406</v>
       </c>
       <c r="C21">
         <v>338.08353538342624</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>16.82232736696669</v>
+        <v>11.341790575290101</v>
       </c>
       <c r="B22">
-        <v>-9.9557523465019528</v>
+        <v>-14.796614149658154</v>
       </c>
       <c r="C22">
         <v>338.08353538342624</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>16.502254657424892</v>
+        <v>9.8552453259397144</v>
       </c>
       <c r="B23">
-        <v>-13.476074120569642</v>
+        <v>-18.000209824735741</v>
       </c>
       <c r="C23">
         <v>338.08353538342624</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>16.032848687637831</v>
+        <v>8.2462890737282883</v>
       </c>
       <c r="B24">
-        <v>-16.999556261988666</v>
+        <v>-21.161757420164914</v>
       </c>
       <c r="C24">
         <v>338.08353538342624</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>15.412400932559406</v>
+        <v>6.5136224226878614</v>
       </c>
       <c r="B25">
-        <v>-20.52623492858994</v>
+        <v>-24.280810594490415</v>
       </c>
       <c r="C25">
         <v>338.08353538342624</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>14.638508899523277</v>
+        <v>4.6554163055878837</v>
       </c>
       <c r="B26">
-        <v>-24.05616096476923</v>
+        <v>-27.356741064610279</v>
       </c>
       <c r="C26">
         <v>338.08353538342624</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>13.705994225382167</v>
+        <v>2.6677229701475533</v>
       </c>
       <c r="B27">
-        <v>-27.589443961181669</v>
+        <v>-30.388192780835706</v>
       </c>
       <c r="C27">
         <v>338.08353538342624</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>12.60898457936854</v>
+        <v>0.54606499282351328</v>
       </c>
       <c r="B28">
-        <v>-31.126208195047237</v>
+        <v>-33.373627751831194</v>
       </c>
       <c r="C28">
         <v>338.08353538342624</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>11.341607630714863</v>
+        <v>-1.714035049927582</v>
       </c>
       <c r="B29">
-        <v>-34.666577943585921</v>
+        <v>-36.31150798626124</v>
       </c>
       <c r="C29">
         <v>338.08353538342624</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>9.8993479729965177</v>
+        <v>-4.1155709906472229</v>
       </c>
       <c r="B30">
-        <v>-38.210648767177361</v>
+        <v>-39.200805105089508</v>
       </c>
       <c r="C30">
         <v>338.08353538342624</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>8.2831178971605</v>
+        <v>-6.6556022978693443</v>
       </c>
       <c r="B31">
-        <v>-41.758401358839834</v>
+        <v>-42.042529178476372</v>
       </c>
       <c r="C31">
         <v>338.08353538342624</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>6.4951866184966986</v>
+        <v>-9.329704849126049</v>
       </c>
       <c r="B32">
-        <v>-45.309787694751321</v>
+        <v>-44.838199888881441</v>
       </c>
       <c r="C32">
         <v>338.08353538342624</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>4.5378233522950184</v>
+        <v>-12.133454521949396</v>
       </c>
       <c r="B33">
-        <v>-48.864759751089771</v>
+        <v>-47.589336918764239</v>
       </c>
       <c r="C33">
         <v>338.08353538342624</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>2.4095665352146547</v>
+        <v>-15.065483535858142</v>
       </c>
       <c r="B34">
-        <v>-52.423348459189953</v>
+        <v>-50.296410099604579</v>
       </c>
       <c r="C34">
         <v>338.08353538342624</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>0.094031489391995737</v>
+        <v>-18.136649478317743</v>
       </c>
       <c r="B35">
-        <v>-55.98590057101385</v>
+        <v>-52.955689858963162</v>
       </c>
       <c r="C35">
         <v>338.08353538342624</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-2.4288972416672596</v>
+        <v>-21.360866278780332</v>
       </c>
       <c r="B36">
-        <v>-59.55284179368028</v>
+        <v>-55.5623967734209</v>
       </c>
       <c r="C36">
         <v>338.08353538342624</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-5.1793351144574533</v>
+        <v>-24.752047866698067</v>
       </c>
       <c r="B37">
-        <v>-63.124597834308069</v>
+        <v>-58.111751419558743</v>
       </c>
       <c r="C37">
         <v>338.08353538342624</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-8.1861072827933423</v>
+        <v>-28.331291304875986</v>
       </c>
       <c r="B38">
-        <v>-66.701778724948085</v>
+        <v>-60.596506973509214</v>
       </c>
       <c r="C38">
         <v>338.08353538342624</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-11.512877689771523</v>
+        <v>-32.148426189530824</v>
       </c>
       <c r="B39">
-        <v>-70.285731797379555</v>
+        <v>-62.99954700961122</v>
       </c>
       <c r="C39">
         <v>338.08353538342624</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-15.232019975809033</v>
+        <v>-36.260465250232222</v>
       </c>
       <c r="B40">
-        <v>-73.877988708313737</v>
+        <v>-65.301287701755285</v>
       </c>
       <c r="C40">
         <v>338.08353538342624</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-19.415907781322897</v>
+        <v>-40.724421216549828</v>
       </c>
       <c r="B41">
-        <v>-77.4800811144619</v>
+        <v>-67.482145223831921</v>
       </c>
       <c r="C41">
         <v>338.08353538342624</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-19.415907781322897</v>
+        <v>-40.724421216549828</v>
       </c>
       <c r="B42">
-        <v>-77.4800811144619</v>
+        <v>-67.482145223831921</v>
       </c>
       <c r="C42">
         <v>338.08353538342624</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-17.698200515303338</v>
+        <v>-38.593401186442215</v>
       </c>
       <c r="B43">
-        <v>-73.930180942292324</v>
+        <v>-64.499926110332211</v>
       </c>
       <c r="C43">
         <v>338.08353538342624</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-16.021691765564743</v>
+        <v>-36.413634765568133</v>
       </c>
       <c r="B44">
-        <v>-70.381152661927459</v>
+        <v>-61.534451342304848</v>
       </c>
       <c r="C44">
         <v>338.08353538342624</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-14.418386600387647</v>
+        <v>-34.226848483952324</v>
       </c>
       <c r="B45">
-        <v>-66.833673602535</v>
+        <v>-58.571387890717105</v>
       </c>
       <c r="C45">
         <v>338.08353538342624</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-12.920290088052601</v>
+        <v>-32.074768871619568</v>
       </c>
       <c r="B46">
-        <v>-63.288421093282629</v>
+        <v>-55.596402726536247</v>
       </c>
       <c r="C46">
         <v>338.08353538342624</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-11.553997449586852</v>
+        <v>-29.992948908439747</v>
       </c>
       <c r="B47">
-        <v>-59.745957973742051</v>
+        <v>-52.59728343017278</v>
       </c>
       <c r="C47">
         <v>338.08353538342624</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-10.3244645170045</v>
+        <v>-27.992247373663474</v>
       </c>
       <c r="B48">
-        <v>-56.206389125100962</v>
+        <v>-49.5703000198102</v>
       </c>
       <c r="C48">
         <v>338.08353538342624</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-9.2312372750663414</v>
+        <v>-26.077349496386468</v>
       </c>
       <c r="B49">
-        <v>-52.669704938951014</v>
+        <v>-46.513843123075233</v>
       </c>
       <c r="C49">
         <v>338.08353538342624</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-8.2738617085331931</v>
+        <v>-24.252940505704494</v>
       </c>
       <c r="B50">
-        <v>-49.13589580688393</v>
+        <v>-43.4263033675946</v>
       </c>
       <c r="C50">
         <v>338.08353538342624</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-7.4498591560382614</v>
+        <v>-22.521317506233792</v>
       </c>
       <c r="B51">
-        <v>-45.60490927253165</v>
+        <v>-40.306891699806066</v>
       </c>
       <c r="C51">
         <v>338.08353538342624</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-6.7486523717043347</v>
+        <v>-20.875225104672644</v>
       </c>
       <c r="B52">
-        <v>-42.076521487687295</v>
+        <v>-37.15810034139151</v>
       </c>
       <c r="C52">
         <v>338.08353538342624</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-6.157639463526607</v>
+        <v>-19.305019783239821</v>
       </c>
       <c r="B53">
-        <v>-38.550465756184238</v>
+        <v>-33.983241832843873</v>
       </c>
       <c r="C53">
         <v>338.08353538342624</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-5.66421853950026</v>
+        <v>-17.801058024154081</v>
       </c>
       <c r="B54">
-        <v>-35.026475381855832</v>
+        <v>-30.785628714656056</v>
       </c>
       <c r="C54">
         <v>338.08353538342624</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-5.25799754520102</v>
+        <v>-16.355586772937691</v>
       </c>
       <c r="B55">
-        <v>-31.504330435736097</v>
+        <v>-27.567924154718025</v>
       </c>
       <c r="C55">
         <v>338.08353538342624</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-4.93742377652673</v>
+        <v>-14.968414828326855</v>
       </c>
       <c r="B56">
-        <v>-27.983998057661495</v>
+        <v>-24.330193830507969</v>
       </c>
       <c r="C56">
         <v>338.08353538342624</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-4.7031543669557738</v>
+        <v>-13.64124145236126</v>
       </c>
       <c r="B57">
-        <v>-24.465492154669136</v>
+        <v>-21.071854046901105</v>
       </c>
       <c r="C57">
         <v>338.08353538342624</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-4.5558464499665305</v>
+        <v>-12.375765907080599</v>
       </c>
       <c r="B58">
-        <v>-20.948826633796116</v>
+        <v>-17.792321108772676</v>
       </c>
       <c r="C58">
         <v>338.08353538342624</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.4960658488794758</v>
+        <v>-11.17347427557028</v>
       </c>
       <c r="B59">
-        <v>-17.43401346966581</v>
+        <v>-14.491084547794831</v>
       </c>
       <c r="C59">
         <v>338.08353538342624</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.52401314638347</v>
+        <v>-10.034999925098576</v>
       </c>
       <c r="B60">
-        <v>-13.921056907246692</v>
+        <v>-11.167926802827479</v>
       </c>
       <c r="C60">
         <v>338.08353538342624</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-4.6397976150094591</v>
+        <v>-8.9607630439794939</v>
       </c>
       <c r="B61">
-        <v>-10.4099592590935</v>
+        <v>-7.8227035395274456</v>
       </c>
       <c r="C61">
         <v>338.08353538342624</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-4.8435285272884</v>
+        <v>-7.9511838205270289</v>
       </c>
       <c r="B62">
-        <v>-6.9007228377609771</v>
+        <v>-4.4552704235515685</v>
       </c>
       <c r="C62">
         <v>338.08353538342624</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-5.133198554775162</v>
+        <v>-7.00457139596799</v>
       </c>
       <c r="B63">
-        <v>-3.3933051617867149</v>
+        <v>-1.066208263509429</v>
       </c>
       <c r="C63">
         <v>338.08353538342624</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-5.4983339651203336</v>
+        <v>-6.11079072318043</v>
       </c>
       <c r="B64">
-        <v>0.11251542636029623</v>
+        <v>2.3410015601783911</v>
       </c>
       <c r="C64">
         <v>338.08353538342624</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-5.92634442499841</v>
+        <v>-5.2575957079552111</v>
       </c>
       <c r="B65">
-        <v>3.61700537822821</v>
+        <v>5.7621525241385534</v>
       </c>
       <c r="C65">
         <v>338.08353538342624</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-6.4046396010838968</v>
+        <v>-4.43274025608319</v>
       </c>
       <c r="B66">
-        <v>7.1204311453652025</v>
+        <v>9.19303810499774</v>
       </c>
       <c r="C66">
         <v>338.08353538342624</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-6.9382202399923587</v>
+        <v>-3.6405192240735529</v>
       </c>
       <c r="B67">
-        <v>10.622686896047574</v>
+        <v>12.635133582464109</v>
       </c>
       <c r="C67">
         <v>338.08353538342624</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-7.60245140810358</v>
+        <v>-2.9513912713087502</v>
       </c>
       <c r="B68">
-        <v>14.122177665464223</v>
+        <v>16.112641448571779</v>
       </c>
       <c r="C68">
         <v>338.08353538342624</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-8.45654544146324</v>
+        <v>-2.4203720073090151</v>
       </c>
       <c r="B69">
-        <v>17.617650332017686</v>
+        <v>19.644459520322055</v>
       </c>
       <c r="C69">
         <v>338.08353538342624</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-9.4247394350162654</v>
+        <v>-1.9745410392724427</v>
       </c>
       <c r="B70">
-        <v>21.110708280052371</v>
+        <v>23.205539702258942</v>
       </c>
       <c r="C70">
         <v>338.08353538342624</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-10.424529584790928</v>
+        <v>-1.5344301646656369</v>
       </c>
       <c r="B71">
-        <v>24.603097552800747</v>
+        <v>26.768584731623829</v>
       </c>
       <c r="C71">
         <v>338.08353538342624</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-11.481423732249501</v>
+        <v>-1.1223159443513997</v>
       </c>
       <c r="B72">
-        <v>28.094278323105566</v>
+        <v>30.341246588905079</v>
       </c>
       <c r="C72">
         <v>338.08353538342624</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-12.635696804659457</v>
+        <v>-0.77418824818595822</v>
       </c>
       <c r="B73">
-        <v>31.583398245246897</v>
+        <v>33.935887765046147</v>
       </c>
       <c r="C73">
         <v>338.08353538342624</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-13.878680427075032</v>
+        <v>-0.47914541860306392</v>
       </c>
       <c r="B74">
-        <v>35.070640769643767</v>
+        <v>37.548763549564072</v>
       </c>
       <c r="C74">
         <v>338.08353538342624</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-15.189587312854545</v>
+        <v>-0.21445952270166685</v>
       </c>
       <c r="B75">
-        <v>38.556445821480423</v>
+        <v>41.172066916043477</v>
       </c>
       <c r="C75">
         <v>338.08353538342624</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-16.548097830785871</v>
+        <v>0.043010946336043826</v>
       </c>
       <c r="B76">
-        <v>42.0412434288629</v>
+        <v>44.797848775765907</v>
       </c>
       <c r="C76">
         <v>338.08353538342624</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-17.937021253915066</v>
+        <v>0.31403580312706558</v>
       </c>
       <c r="B77">
-        <v>45.5253974023189</v>
+        <v>48.418974714349581</v>
       </c>
       <c r="C77">
         <v>338.08353538342624</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-19.351214816891307</v>
+        <v>0.60948451956847716</v>
       </c>
       <c r="B78">
-        <v>49.009016579140805</v>
+        <v>52.031711077062631</v>
       </c>
       <c r="C78">
         <v>338.08353538342624</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-20.775024493616769</v>
+        <v>0.95099962067164356</v>
       </c>
       <c r="B79">
-        <v>52.492432248372438</v>
+        <v>55.628623674214573</v>
       </c>
       <c r="C79">
         <v>338.08353538342624</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-22.174512805480891</v>
+        <v>1.3796621531026316</v>
       </c>
       <c r="B80">
-        <v>55.976362635138017</v>
+        <v>59.195601199779972</v>
       </c>
       <c r="C80">
         <v>338.08353538342624</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-23.445967256288942</v>
+        <v>2.0048829620297819</v>
       </c>
       <c r="B81">
-        <v>59.463002626138312</v>
+        <v>62.695061117675337</v>
       </c>
       <c r="C81">
         <v>338.08353538342624</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-22.388890849241182</v>
+        <v>4.9228764936436535</v>
       </c>
       <c r="B82">
-        <v>62.998921745496553</v>
+        <v>65.406955475237083</v>
       </c>
       <c r="C82">
         <v>338.08353538342624</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-64.590916328643459</v>
+        <v>-56.713154902498772</v>
       </c>
       <c r="B1">
-        <v>52.464598990812654</v>
+        <v>49.093245000695426</v>
       </c>
       <c r="C1">
         <v>592.998505179033</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-60.5339545865562</v>
+        <v>-51.941891147328739</v>
       </c>
       <c r="B2">
-        <v>50.668340646226348</v>
+        <v>47.976346149999536</v>
       </c>
       <c r="C2">
         <v>592.998505179033</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-56.55448157421511</v>
+        <v>-48.015808174711687</v>
       </c>
       <c r="B3">
-        <v>48.79463675536099</v>
+        <v>46.030438567086513</v>
       </c>
       <c r="C3">
         <v>592.998505179033</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-52.6382692283064</v>
+        <v>-44.232778855320305</v>
       </c>
       <c r="B4">
-        <v>46.857707452414608</v>
+        <v>43.944214580691806</v>
       </c>
       <c r="C4">
         <v>592.998505179033</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-48.771089485516342</v>
+        <v>-40.553658480622062</v>
       </c>
       <c r="B5">
-        <v>44.871772871585286</v>
+        <v>41.756069887763928</v>
       </c>
       <c r="C5">
         <v>592.998505179033</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-44.944600655846337</v>
+        <v>-36.962421703123844</v>
       </c>
       <c r="B6">
-        <v>42.845170054155581</v>
+        <v>39.481723199947538</v>
       </c>
       <c r="C6">
         <v>592.998505179033</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-41.174006542558651</v>
+        <v>-33.449881478025</v>
       </c>
       <c r="B7">
-        <v>40.762703669746244</v>
+        <v>37.130185773201447</v>
       </c>
       <c r="C7">
         <v>592.998505179033</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-37.475356193176481</v>
+        <v>-30.010597263122662</v>
       </c>
       <c r="B8">
-        <v>38.608333614760717</v>
+        <v>34.706794048068616</v>
       </c>
       <c r="C8">
         <v>592.998505179033</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-33.844534139006271</v>
+        <v>-26.636131452350455</v>
       </c>
       <c r="B9">
-        <v>36.386173064395066</v>
+        <v>32.219824181854605</v>
       </c>
       <c r="C9">
         <v>592.998505179033</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-30.273822728922362</v>
+        <v>-23.317386632323007</v>
       </c>
       <c r="B10">
-        <v>34.103935368827777</v>
+        <v>29.678199514148695</v>
       </c>
       <c r="C10">
         <v>592.998505179033</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-26.761260098287497</v>
+        <v>-20.045623224242568</v>
       </c>
       <c r="B11">
-        <v>31.763581299374309</v>
+        <v>27.090492396912506</v>
       </c>
       <c r="C11">
         <v>592.998505179033</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-23.306323329086521</v>
+        <v>-16.816145038046265</v>
       </c>
       <c r="B12">
-        <v>29.365633482634365</v>
+        <v>24.461309161301013</v>
       </c>
       <c r="C12">
         <v>592.998505179033</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-19.908489503304295</v>
+        <v>-13.640071604023284</v>
       </c>
       <c r="B13">
-        <v>26.910614545207654</v>
+        <v>21.779743042870262</v>
       </c>
       <c r="C13">
         <v>592.998505179033</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-16.567233382954683</v>
+        <v>-10.524033037693084</v>
       </c>
       <c r="B14">
-        <v>24.399049432371964</v>
+        <v>19.039290789564919</v>
       </c>
       <c r="C14">
         <v>592.998505179033</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-13.2820204501676</v>
+        <v>-7.4408860751443777</v>
       </c>
       <c r="B15">
-        <v>21.831472364117477</v>
+        <v>16.266576294483194</v>
       </c>
       <c r="C15">
         <v>592.998505179033</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-10.052313867101981</v>
+        <v>-4.3657351716420107</v>
       </c>
       <c r="B16">
-        <v>19.208419879112487</v>
+        <v>13.486018740366555</v>
       </c>
       <c r="C16">
         <v>592.998505179033</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-6.87757679591675</v>
+        <v>-1.3164490385860665</v>
       </c>
       <c r="B17">
-        <v>16.530428516025257</v>
+        <v>10.680091323376175</v>
       </c>
       <c r="C17">
         <v>592.998505179033</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-3.7574498180441847</v>
+        <v>1.6838815004949979</v>
       </c>
       <c r="B18">
-        <v>13.797857493124202</v>
+        <v>7.826145049670358</v>
       </c>
       <c r="C18">
         <v>592.998505179033</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-0.69228319200995325</v>
+        <v>4.6340414296945882</v>
       </c>
       <c r="B19">
-        <v>11.010356747078225</v>
+        <v>4.922988151976198</v>
       </c>
       <c r="C19">
         <v>592.998505179033</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>2.317395404386986</v>
+        <v>7.5382846850116065</v>
       </c>
       <c r="B20">
-        <v>8.1673988941563369</v>
+        <v>1.9747931696629655</v>
       </c>
       <c r="C20">
         <v>592.998505179033</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>5.2710582933476191</v>
+        <v>10.400865202444916</v>
       </c>
       <c r="B21">
-        <v>5.2684565506275813</v>
+        <v>-1.0142673579000361</v>
       </c>
       <c r="C21">
         <v>592.998505179033</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>8.1683536896726388</v>
+        <v>13.225277510874621</v>
       </c>
       <c r="B22">
-        <v>2.3131781273379532</v>
+        <v>-4.04076576764194</v>
       </c>
       <c r="C22">
         <v>592.998505179033</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>11.009633378561361</v>
+        <v>16.011978510705635</v>
       </c>
       <c r="B23">
-        <v>-0.69808478655855344</v>
+        <v>-7.1042539016854533</v>
       </c>
       <c r="C23">
         <v>592.998505179033</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>13.79542503781277</v>
+        <v>18.76066569522407</v>
       </c>
       <c r="B24">
-        <v>-3.7648048073309504</v>
+        <v>-10.205028478451682</v>
       </c>
       <c r="C24">
         <v>592.998505179033</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>16.526256345225871</v>
+        <v>21.471036557716065</v>
       </c>
       <c r="B25">
-        <v>-6.8864545512482858</v>
+        <v>-13.343386216361768</v>
       </c>
       <c r="C25">
         <v>592.998505179033</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>19.20247755932629</v>
+        <v>24.142659516567356</v>
       </c>
       <c r="B26">
-        <v>-10.062683954979439</v>
+        <v>-16.519750438962866</v>
       </c>
       <c r="C26">
         <v>592.998505179033</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>21.823729261546326</v>
+        <v>26.774586690562188</v>
       </c>
       <c r="B27">
-        <v>-13.293852236792834</v>
+        <v>-19.735050890306447</v>
       </c>
       <c r="C27">
         <v>592.998505179033</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>24.389474614044889</v>
+        <v>29.365741123584407</v>
       </c>
       <c r="B28">
-        <v>-16.58049593535673</v>
+        <v>-22.990343919569991</v>
       </c>
       <c r="C28">
         <v>592.998505179033</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>26.899176778980934</v>
+        <v>31.915045859517896</v>
       </c>
       <c r="B29">
-        <v>-19.92315158933943</v>
+        <v>-26.286685875931028</v>
       </c>
       <c r="C29">
         <v>592.998505179033</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>29.352301238484362</v>
+        <v>34.421981145698943</v>
       </c>
       <c r="B30">
-        <v>-23.3223534187311</v>
+        <v>-29.624586566883632</v>
       </c>
       <c r="C30">
         <v>592.998505179033</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>31.748322754569035</v>
+        <v>36.888256043273536</v>
       </c>
       <c r="B31">
-        <v>-26.77862636880953</v>
+        <v>-33.002369633188209</v>
       </c>
       <c r="C31">
         <v>592.998505179033</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>34.086718409219841</v>
+        <v>39.316136816840206</v>
       </c>
       <c r="B32">
-        <v>-30.292493066174462</v>
+        <v>-36.41781217392181</v>
       </c>
       <c r="C32">
         <v>592.998505179033</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>36.366965284421575</v>
+        <v>41.707889730997358</v>
       </c>
       <c r="B33">
-        <v>-33.864476137425548</v>
+        <v>-39.868691288161372</v>
       </c>
       <c r="C33">
         <v>592.998505179033</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>38.587101515537007</v>
+        <v>44.064867352074764</v>
       </c>
       <c r="B34">
-        <v>-37.496536353878284</v>
+        <v>-43.353680290159438</v>
       </c>
       <c r="C34">
         <v>592.998505179033</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>40.739409451440508</v>
+        <v>46.384767453327356</v>
       </c>
       <c r="B35">
-        <v>-41.196387065711143</v>
+        <v>-46.875037354870564</v>
       </c>
       <c r="C35">
         <v>592.998505179033</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>42.819773623438472</v>
+        <v>48.664374109741296</v>
       </c>
       <c r="B36">
-        <v>-44.9681414481202</v>
+        <v>-50.435916872424748</v>
       </c>
       <c r="C36">
         <v>592.998505179033</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>44.844243079054131</v>
+        <v>50.900471396302812</v>
       </c>
       <c r="B37">
-        <v>-48.795759397508867</v>
+        <v>-54.039473232952076</v>
       </c>
       <c r="C37">
         <v>592.998505179033</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>46.8280216215497</v>
+        <v>53.087610685248855</v>
       </c>
       <c r="B38">
-        <v>-52.664045583497924</v>
+        <v>-57.691050807843148</v>
       </c>
       <c r="C38">
         <v>592.998505179033</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>48.762767560926662</v>
+        <v>55.211412537819385</v>
       </c>
       <c r="B39">
-        <v>-56.581337047369942</v>
+        <v>-61.404753893530831</v>
       </c>
       <c r="C39">
         <v>592.998505179033</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>50.634252833871216</v>
+        <v>57.255264812505061</v>
       </c>
       <c r="B40">
-        <v>-60.561853923322964</v>
+        <v>-65.196876767708474</v>
       </c>
       <c r="C40">
         <v>592.998505179033</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>52.428249377069619</v>
+        <v>59.202555367796592</v>
       </c>
       <c r="B41">
-        <v>-64.619816345555037</v>
+        <v>-69.08371370806951</v>
       </c>
       <c r="C41">
         <v>592.998505179033</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>51.795993534253228</v>
+        <v>59.202555367796592</v>
       </c>
       <c r="B42">
-        <v>-65.2517198403659</v>
+        <v>-69.08371370806951</v>
       </c>
       <c r="C42">
         <v>592.998505179033</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>49.357722080479519</v>
+        <v>56.477268519863244</v>
       </c>
       <c r="B43">
-        <v>-61.837673282632544</v>
+        <v>-65.959986546760049</v>
       </c>
       <c r="C43">
         <v>592.998505179033</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>46.908150421998606</v>
+        <v>53.789034662800695</v>
       </c>
       <c r="B44">
-        <v>-58.43492063214844</v>
+        <v>-62.799915382344096</v>
       </c>
       <c r="C44">
         <v>592.998505179033</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>44.433955954146271</v>
+        <v>51.121537996673162</v>
       </c>
       <c r="B45">
-        <v>-55.056777069062441</v>
+        <v>-59.619503821267827</v>
       </c>
       <c r="C45">
         <v>592.998505179033</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>41.921816072258395</v>
+        <v>48.4584627215449</v>
       </c>
       <c r="B46">
-        <v>-51.716557773523462</v>
+        <v>-56.434755469977461</v>
       </c>
       <c r="C46">
         <v>592.998505179033</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>39.364266070263085</v>
+        <v>45.785714572024631</v>
       </c>
       <c r="B47">
-        <v>-48.421723291619188</v>
+        <v>-53.259494908166154</v>
       </c>
       <c r="C47">
         <v>592.998505179033</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>36.777272836457826</v>
+        <v>43.098085420899146</v>
       </c>
       <c r="B48">
-        <v>-45.15631563319247</v>
+        <v>-50.098830608515</v>
       </c>
       <c r="C48">
         <v>592.998505179033</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>34.177606789987479</v>
+        <v>40.392588675499688</v>
       </c>
       <c r="B49">
-        <v>-41.9035737250362</v>
+        <v>-46.955692016952071</v>
       </c>
       <c r="C49">
         <v>592.998505179033</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>31.561820879017045</v>
+        <v>37.6662377431576</v>
       </c>
       <c r="B50">
-        <v>-38.666942697988013</v>
+        <v>-43.833008579405472</v>
       </c>
       <c r="C50">
         <v>592.998505179033</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>28.922822601921045</v>
+        <v>34.9169479741883</v>
       </c>
       <c r="B51">
-        <v>-35.453511101113911</v>
+        <v>-40.732825056981675</v>
       </c>
       <c r="C51">
         <v>592.998505179033</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>26.259155128892118</v>
+        <v>32.146242490843861</v>
       </c>
       <c r="B52">
-        <v>-32.264734952348789</v>
+        <v>-37.653647471500733</v>
       </c>
       <c r="C52">
         <v>592.998505179033</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>23.570770548077508</v>
+        <v>29.356546358360635</v>
       </c>
       <c r="B53">
-        <v>-29.100662136844861</v>
+        <v>-34.593097159961147</v>
       </c>
       <c r="C53">
         <v>592.998505179033</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>20.857620947624358</v>
+        <v>26.550284641974805</v>
       </c>
       <c r="B54">
-        <v>-25.961340539754222</v>
+        <v>-31.548795459361351</v>
       </c>
       <c r="C54">
         <v>592.998505179033</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>18.119622160208003</v>
+        <v>23.729314417994139</v>
       </c>
       <c r="B55">
-        <v>-22.846854281496221</v>
+        <v>-28.518920827485452</v>
       </c>
       <c r="C55">
         <v>592.998505179033</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>15.356544996616263</v>
+        <v>20.893220807012156</v>
       </c>
       <c r="B56">
-        <v>-19.757432423558864</v>
+        <v>-25.503880205260057</v>
       </c>
       <c r="C56">
         <v>592.998505179033</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>12.568124012165065</v>
+        <v>18.041020940693798</v>
       </c>
       <c r="B57">
-        <v>-16.6933402626973</v>
+        <v>-22.504637654397353</v>
       </c>
       <c r="C57">
         <v>592.998505179033</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>9.7540937621703634</v>
+        <v>15.171731950704062</v>
       </c>
       <c r="B58">
-        <v>-13.654843095666731</v>
+        <v>-19.522157236609587</v>
       </c>
       <c r="C58">
         <v>592.998505179033</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>6.9143360231994935</v>
+        <v>12.284489622305207</v>
       </c>
       <c r="B59">
-        <v>-10.642059080015379</v>
+        <v>-16.55728663038029</v>
       </c>
       <c r="C59">
         <v>592.998505179033</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>4.0493214568254716</v>
+        <v>9.3789043551487978</v>
       </c>
       <c r="B60">
-        <v>-7.6545178164638834</v>
+        <v>-13.610407981278334</v>
       </c>
       <c r="C60">
         <v>592.998505179033</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>1.1596679458726857</v>
+        <v>6.4547052024836891</v>
       </c>
       <c r="B61">
-        <v>-4.6916017665259231</v>
+        <v>-10.681787051643896</v>
       </c>
       <c r="C61">
         <v>592.998505179033</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-1.7540066268344432</v>
+        <v>3.5116212175587562</v>
       </c>
       <c r="B62">
-        <v>-1.7526933917152039</v>
+        <v>-7.7716896038171734</v>
       </c>
       <c r="C62">
         <v>592.998505179033</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-4.6912903394129675</v>
+        <v>0.5501301320392773</v>
       </c>
       <c r="B63">
-        <v>1.1626190002924615</v>
+        <v>-4.879647047254779</v>
       </c>
       <c r="C63">
         <v>592.998505179033</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-7.6525951137458446</v>
+        <v>-2.4262956087438741</v>
       </c>
       <c r="B64">
-        <v>4.0539237171728937</v>
+        <v>-2.0022533798789346</v>
       </c>
       <c r="C64">
         <v>592.998505179033</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-10.638538832657464</v>
+        <v>-5.4134348810433792</v>
       </c>
       <c r="B65">
-        <v>6.9206032204397712</v>
+        <v>0.86463175327168751</v>
       </c>
       <c r="C65">
         <v>592.998505179033</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-13.649739378972255</v>
+        <v>-8.4070665611119626</v>
       </c>
       <c r="B66">
-        <v>9.7620399716068142</v>
+        <v>3.725148707158453</v>
       </c>
       <c r="C66">
         <v>592.998505179033</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-16.686667414263209</v>
+        <v>-11.408447155679166</v>
       </c>
       <c r="B67">
-        <v>12.577763571394623</v>
+        <v>6.578065017588612</v>
       </c>
       <c r="C67">
         <v>592.998505179033</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-19.749204715097662</v>
+        <v>-14.440743693381942</v>
       </c>
       <c r="B68">
-        <v>15.367892177351447</v>
+        <v>9.4006569437530576</v>
       </c>
       <c r="C68">
         <v>592.998505179033</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-22.837085836791573</v>
+        <v>-17.521913692842968</v>
       </c>
       <c r="B69">
-        <v>18.132691086232473</v>
+        <v>12.175310573865765</v>
       </c>
       <c r="C69">
         <v>592.998505179033</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-25.950045334660874</v>
+        <v>-20.6271661107203</v>
       </c>
       <c r="B70">
-        <v>20.872425594792855</v>
+        <v>14.926342588849316</v>
       </c>
       <c r="C70">
         <v>592.998505179033</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-29.087854019493378</v>
+        <v>-23.72947190035859</v>
       </c>
       <c r="B71">
-        <v>23.587324764520606</v>
+        <v>17.680264850027758</v>
       </c>
       <c r="C71">
         <v>592.998505179033</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-32.250427723964414</v>
+        <v>-26.835598563813367</v>
       </c>
       <c r="B72">
-        <v>26.277472715835049</v>
+        <v>20.430439347622418</v>
       </c>
       <c r="C72">
         <v>592.998505179033</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-35.437718536221155</v>
+        <v>-29.956814281410836</v>
       </c>
       <c r="B73">
-        <v>28.942917333888328</v>
+        <v>23.165813511485617</v>
       </c>
       <c r="C73">
         <v>592.998505179033</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-38.649678544410811</v>
+        <v>-33.088593397849024</v>
       </c>
       <c r="B74">
-        <v>31.583706503832605</v>
+        <v>25.890826401096476</v>
       </c>
       <c r="C74">
         <v>592.998505179033</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-41.884850918726016</v>
+        <v>-36.222378034713273</v>
       </c>
       <c r="B75">
-        <v>34.201296243602791</v>
+        <v>28.613872144766283</v>
       </c>
       <c r="C75">
         <v>592.998505179033</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-45.136143157541341</v>
+        <v>-39.349275256766539</v>
       </c>
       <c r="B76">
-        <v>36.802775102264917</v>
+        <v>31.343673516508311</v>
       </c>
       <c r="C76">
         <v>592.998505179033</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-48.400108209021731</v>
+        <v>-42.461063761482833</v>
       </c>
       <c r="B77">
-        <v>39.391588210656586</v>
+        <v>34.088294508932094</v>
       </c>
       <c r="C77">
         <v>592.998505179033</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-51.693516492312078</v>
+        <v>-45.552543834002819</v>
       </c>
       <c r="B78">
-        <v>41.950974495570691</v>
+        <v>36.852835343330433</v>
       </c>
       <c r="C78">
         <v>592.998505179033</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-55.03233489570983</v>
+        <v>-48.614780484241308</v>
       </c>
       <c r="B79">
-        <v>44.464975966850091</v>
+        <v>39.646060043869255</v>
       </c>
       <c r="C79">
         <v>592.998505179033</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-58.409098713143173</v>
+        <v>-51.632023111199892</v>
       </c>
       <c r="B80">
-        <v>46.9410531705825</v>
+        <v>42.483417832815469</v>
       </c>
       <c r="C80">
         <v>592.998505179033</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-61.810485339947896</v>
+        <v>-54.565419630663321</v>
       </c>
       <c r="B81">
-        <v>49.392521286916768</v>
+        <v>45.403017381998986</v>
       </c>
       <c r="C81">
         <v>592.998505179033</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-65.223172171459836</v>
+        <v>-56.713154902498772</v>
       </c>
       <c r="B82">
-        <v>51.8326954960018</v>
+        <v>49.093245000695426</v>
       </c>
       <c r="C82">
         <v>592.998505179033</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>-85.354737784071048</v>
+        <v>-84.756279050194436</v>
       </c>
       <c r="B1">
-        <v>32.509648010010793</v>
+        <v>34.028419621882058</v>
       </c>
       <c r="C1">
         <v>767.45943045334911</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>-80.960304783689708</v>
+        <v>-80.417149211268082</v>
       </c>
       <c r="B2">
-        <v>31.207512617715853</v>
+        <v>32.580368949972581</v>
       </c>
       <c r="C2">
         <v>767.45943045334911</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>-76.577906422614191</v>
+        <v>-76.087899936536147</v>
       </c>
       <c r="B3">
-        <v>29.874666476677184</v>
+        <v>31.10761244899388</v>
       </c>
       <c r="C3">
         <v>767.45943045334911</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>-72.203621812758627</v>
+        <v>-71.764541076818645</v>
       </c>
       <c r="B4">
-        <v>28.521115155470422</v>
+        <v>29.620127276288525</v>
       </c>
       <c r="C4">
         <v>767.45943045334911</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>-67.833530066037113</v>
+        <v>-67.443082482935651</v>
       </c>
       <c r="B5">
-        <v>27.1568642226712</v>
+        <v>28.12789058919909</v>
       </c>
       <c r="C5">
         <v>767.45943045334911</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>-63.465381551795566</v>
+        <v>-63.121234922426233</v>
       </c>
       <c r="B6">
-        <v>25.787654427131994</v>
+        <v>26.636626492621385</v>
       </c>
       <c r="C6">
         <v>767.45943045334911</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>-59.103611669106911</v>
+        <v>-58.803512829705774</v>
       </c>
       <c r="B7">
-        <v>24.402167238812478</v>
+        <v>25.135046881664167</v>
       </c>
       <c r="C7">
         <v>767.45943045334911</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>-54.752890456093532</v>
+        <v>-54.494669430437121</v>
       </c>
       <c r="B8">
-        <v>22.988485361003125</v>
+        <v>23.611266566530453</v>
       </c>
       <c r="C8">
         <v>767.45943045334911</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>-50.412141477348563</v>
+        <v>-50.193609448396252</v>
       </c>
       <c r="B9">
-        <v>21.549355709209944</v>
+        <v>22.068024227587131</v>
       </c>
       <c r="C9">
         <v>767.45943045334911</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-46.079256950423826</v>
+        <v>-45.898187936627039</v>
       </c>
       <c r="B10">
-        <v>20.090157055120859</v>
+        <v>20.510683191443686</v>
       </c>
       <c r="C10">
         <v>767.45943045334911</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-41.753750178235087</v>
+        <v>-41.607909767131581</v>
       </c>
       <c r="B11">
-        <v>18.612131382935743</v>
+        <v>18.940481499515904</v>
       </c>
       <c r="C11">
         <v>767.45943045334911</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-37.43553973503905</v>
+        <v>-37.32269226665148</v>
       </c>
       <c r="B12">
-        <v>17.11548647998243</v>
+        <v>17.357625871921154</v>
       </c>
       <c r="C12">
         <v>767.45943045334911</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-33.124544195092454</v>
+        <v>-33.042452761928367</v>
       </c>
       <c r="B13">
-        <v>15.600430133588771</v>
+        <v>15.762323028776816</v>
       </c>
       <c r="C13">
         <v>767.45943045334911</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-28.820676656520387</v>
+        <v>-28.767102992861307</v>
       </c>
       <c r="B14">
-        <v>14.067184105419408</v>
+        <v>14.154793659805188</v>
       </c>
       <c r="C14">
         <v>767.45943045334911</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-24.523828312921385</v>
+        <v>-24.4965323519789</v>
       </c>
       <c r="B15">
-        <v>12.516026054486112</v>
+        <v>12.535314333148254</v>
       </c>
       <c r="C15">
         <v>767.45943045334911</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-20.233884881762371</v>
+        <v>-20.230624644967222</v>
       </c>
       <c r="B16">
-        <v>10.947247614137469</v>
+        <v>10.904175586552935</v>
       </c>
       <c r="C16">
         <v>767.45943045334911</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-15.950732080510226</v>
+        <v>-15.9692636775123</v>
       </c>
       <c r="B17">
-        <v>9.3611404177220372</v>
+        <v>9.26166795776613</v>
       </c>
       <c r="C17">
         <v>767.45943045334911</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-11.674301836781089</v>
+        <v>-11.712380272833734</v>
       </c>
       <c r="B18">
-        <v>7.7578781766261509</v>
+        <v>7.607964419674702</v>
       </c>
       <c r="C18">
         <v>767.45943045334911</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-7.4047109187879361</v>
+        <v>-7.4600933242852587</v>
       </c>
       <c r="B19">
-        <v>6.1371629143871136</v>
+        <v>5.9427676857252711</v>
       </c>
       <c r="C19">
         <v>767.45943045334911</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-3.1421223048929607</v>
+        <v>-3.2125687427541405</v>
       </c>
       <c r="B20">
-        <v>4.4985787325799924</v>
+        <v>4.2656629045044037</v>
       </c>
       <c r="C20">
         <v>767.45943045334911</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>1.113301026541629</v>
+        <v>1.0300275608723359</v>
       </c>
       <c r="B21">
-        <v>2.8417097327798517</v>
+        <v>2.5762352245986651</v>
       </c>
       <c r="C21">
         <v>767.45943045334911</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>5.3614504232743982</v>
+        <v>5.267584979336017</v>
       </c>
       <c r="B22">
-        <v>1.1662786493700563</v>
+        <v>0.87420807839908932</v>
       </c>
       <c r="C22">
         <v>767.45943045334911</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>9.6024345375467952</v>
+        <v>9.5002141198950731</v>
       </c>
       <c r="B23">
-        <v>-0.52743725203276359</v>
+        <v>-0.84014196648536132</v>
       </c>
       <c r="C23">
         <v>767.45943045334911</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>13.836416347721015</v>
+        <v>13.728080893436767</v>
       </c>
       <c r="B24">
-        <v>-2.2390220730036687</v>
+        <v>-2.5664000586412508</v>
       </c>
       <c r="C24">
         <v>767.45943045334911</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>18.063558832159249</v>
+        <v>17.951351210848376</v>
       </c>
       <c r="B25">
-        <v>-3.9680599151177223</v>
+        <v>-4.304151346655142</v>
       </c>
       <c r="C25">
         <v>767.45943045334911</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>22.283978759074461</v>
+        <v>22.170143965483614</v>
       </c>
       <c r="B26">
-        <v>-5.7142528019122274</v>
+        <v>-6.0530985439736522</v>
       </c>
       <c r="C26">
         <v>767.45943045334911</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>26.497608056082797</v>
+        <v>26.38438998056208</v>
       </c>
       <c r="B27">
-        <v>-7.477774444773515</v>
+        <v>-7.8134146234836406</v>
       </c>
       <c r="C27">
         <v>767.45943045334911</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>30.704332440651161</v>
+        <v>30.593973061769844</v>
       </c>
       <c r="B28">
-        <v>-9.2589164770501586</v>
+        <v>-9.5853901229320257</v>
       </c>
       <c r="C28">
         <v>767.45943045334911</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>34.904037630246457</v>
+        <v>34.79877701479294</v>
       </c>
       <c r="B29">
-        <v>-11.057970532090733</v>
+        <v>-11.369315580065713</v>
       </c>
       <c r="C29">
         <v>767.45943045334911</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>39.096614818467245</v>
+        <v>38.998691232160013</v>
       </c>
       <c r="B30">
-        <v>-12.875214268907021</v>
+        <v>-13.1654675630267</v>
       </c>
       <c r="C30">
         <v>767.45943045334911</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>43.281977103438543</v>
+        <v>43.193627453770048</v>
       </c>
       <c r="B31">
-        <v>-14.710869449163631</v>
+        <v>-14.974066761537255</v>
       </c>
       <c r="C31">
         <v>767.45943045334911</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>47.460043059417181</v>
+        <v>47.383503006364762</v>
       </c>
       <c r="B32">
-        <v>-16.56514386018846</v>
+        <v>-16.795319895714794</v>
       </c>
       <c r="C32">
         <v>767.45943045334911</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>51.6307312606598</v>
+        <v>51.568235216685714</v>
       </c>
       <c r="B33">
-        <v>-18.438245289309311</v>
+        <v>-18.629433685676659</v>
       </c>
       <c r="C33">
         <v>767.45943045334911</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>55.793555010082216</v>
+        <v>55.747328956735025</v>
       </c>
       <c r="B34">
-        <v>-20.331415720726074</v>
+        <v>-20.477646172838661</v>
       </c>
       <c r="C34">
         <v>767.45943045334911</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>59.946406525236185</v>
+        <v>59.918639279556515</v>
       </c>
       <c r="B35">
-        <v>-22.250033926126651</v>
+        <v>-22.345320683810257</v>
       </c>
       <c r="C35">
         <v>767.45943045334911</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>64.088209370714893</v>
+        <v>64.081070908926236</v>
       </c>
       <c r="B36">
-        <v>-24.196846821017079</v>
+        <v>-24.235195898958356</v>
       </c>
       <c r="C36">
         <v>767.45943045334911</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>68.223633584640723</v>
+        <v>68.239377070506976</v>
       </c>
       <c r="B37">
-        <v>-26.15993710868781</v>
+        <v>-26.135386628485971</v>
       </c>
       <c r="C37">
         <v>767.45943045334911</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>72.357114566086565</v>
+        <v>72.398072198714132</v>
       </c>
       <c r="B38">
-        <v>-28.127986259098527</v>
+        <v>-28.03460476750185</v>
       </c>
       <c r="C38">
         <v>767.45943045334911</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>76.486402684398385</v>
+        <v>76.554867061086824</v>
       </c>
       <c r="B39">
-        <v>-30.106735021101709</v>
+        <v>-29.938574420901819</v>
       </c>
       <c r="C39">
         <v>767.45943045334911</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>80.60757705149021</v>
+        <v>80.705771508445039</v>
       </c>
       <c r="B40">
-        <v>-32.106188963272977</v>
+        <v>-31.857272746028432</v>
       </c>
       <c r="C40">
         <v>767.45943045334911</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>84.71671677927624</v>
+        <v>84.84679539160885</v>
       </c>
       <c r="B41">
-        <v>-34.136353654187964</v>
+        <v>-33.800676900224268</v>
       </c>
       <c r="C41">
         <v>767.45943045334911</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>84.5367725747829</v>
+        <v>84.663656830999159</v>
       </c>
       <c r="B42">
-        <v>-34.595546581509005</v>
+        <v>-34.258605201217129</v>
       </c>
       <c r="C42">
         <v>767.45943045334911</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>80.244267936137277</v>
+        <v>80.336012956734763</v>
       </c>
       <c r="B43">
-        <v>-33.033303991351083</v>
+        <v>-32.781834481135348</v>
       </c>
       <c r="C43">
         <v>767.45943045334911</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>75.958566351217925</v>
+        <v>76.017660616631744</v>
       </c>
       <c r="B44">
-        <v>-31.453700941243419</v>
+        <v>-31.281830770480898</v>
       </c>
       <c r="C44">
         <v>767.45943045334911</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>71.6757476053532</v>
+        <v>71.7046096624404</v>
       </c>
       <c r="B45">
-        <v>-29.866741281300886</v>
+        <v>-29.768571224270197</v>
       </c>
       <c r="C45">
         <v>767.45943045334911</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>67.391891483871518</v>
+        <v>67.392869945911087</v>
       </c>
       <c r="B46">
-        <v>-28.28242886163838</v>
+        <v>-28.252032997519677</v>
       </c>
       <c r="C46">
         <v>767.45943045334911</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>63.104749012314635</v>
+        <v>63.080152235489436</v>
       </c>
       <c r="B47">
-        <v>-26.706502756586463</v>
+        <v>-26.737940192858339</v>
       </c>
       <c r="C47">
         <v>767.45943045334911</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>58.818756177077944</v>
+        <v>58.770970966402473</v>
       </c>
       <c r="B48">
-        <v>-25.127642937338482</v>
+        <v>-25.215004703365565</v>
       </c>
       <c r="C48">
         <v>767.45943045334911</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>54.538583577834011</v>
+        <v>54.470079365088829</v>
       </c>
       <c r="B49">
-        <v>-23.533930674185815</v>
+        <v>-23.671341337304423</v>
       </c>
       <c r="C49">
         <v>767.45943045334911</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>50.263155306510441</v>
+        <v>50.176382156052092</v>
       </c>
       <c r="B50">
-        <v>-21.928111536949196</v>
+        <v>-22.109688773222462</v>
       </c>
       <c r="C50">
         <v>767.45943045334911</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>45.990364077896544</v>
+        <v>45.887734393022356</v>
       </c>
       <c r="B51">
-        <v>-20.315563028434877</v>
+        <v>-20.535410336013452</v>
       </c>
       <c r="C51">
         <v>767.45943045334911</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>41.719723605972852</v>
+        <v>41.603640948570273</v>
       </c>
       <c r="B52">
-        <v>-18.697526083861529</v>
+        <v>-18.949744065671368</v>
       </c>
       <c r="C52">
         <v>767.45943045334911</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>37.451152854517936</v>
+        <v>37.32401914997677</v>
       </c>
       <c r="B53">
-        <v>-17.074207496551008</v>
+        <v>-17.352896680965294</v>
       </c>
       <c r="C53">
         <v>767.45943045334911</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>33.184570787310129</v>
+        <v>33.048786324522595</v>
       </c>
       <c r="B54">
-        <v>-15.445814059825089</v>
+        <v>-15.745074900664235</v>
       </c>
       <c r="C54">
         <v>767.45943045334911</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>28.919890865432816</v>
+        <v>28.777854212609174</v>
       </c>
       <c r="B55">
-        <v>-13.812566609128837</v>
+        <v>-14.126499413234475</v>
       </c>
       <c r="C55">
         <v>767.45943045334911</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>24.657004539188726</v>
+        <v>24.511112207119869</v>
       </c>
       <c r="B56">
-        <v>-12.174742148400128</v>
+        <v>-12.497446785931041</v>
       </c>
       <c r="C56">
         <v>767.45943045334911</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>20.395797756185466</v>
+        <v>20.248444114058543</v>
       </c>
       <c r="B57">
-        <v>-10.532631723700058</v>
+        <v>-10.858207555706171</v>
       </c>
       <c r="C57">
         <v>767.45943045334911</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>16.136156464030623</v>
+        <v>15.989733739429061</v>
       </c>
       <c r="B58">
-        <v>-8.8865263810897233</v>
+        <v>-9.20907225951209</v>
       </c>
       <c r="C58">
         <v>767.45943045334911</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>11.878012795028162</v>
+        <v>11.734911906733737</v>
       </c>
       <c r="B59">
-        <v>-7.2365993096200985</v>
+        <v>-7.550213869528644</v>
       </c>
       <c r="C59">
         <v>767.45943045334911</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>7.6214836202675968</v>
+        <v>7.4840975094688336</v>
       </c>
       <c r="B60">
-        <v>-5.5825522703017407</v>
+        <v>-5.88133509884612</v>
       </c>
       <c r="C60">
         <v>767.45943045334911</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>3.3667319955348054</v>
+        <v>3.2374564586290639</v>
       </c>
       <c r="B61">
-        <v>-3.9239691671350836</v>
+        <v>-4.2020210957824169</v>
       </c>
       <c r="C61">
         <v>767.45943045334911</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-0.8860790233843332</v>
+        <v>-1.004845334790853</v>
       </c>
       <c r="B62">
-        <v>-2.260433904120565</v>
+        <v>-2.5118570086554319</v>
       </c>
       <c r="C62">
         <v>767.45943045334911</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-5.136840732632554</v>
+        <v>-5.2426972634610944</v>
       </c>
       <c r="B63">
-        <v>-0.59166908392514739</v>
+        <v>-0.81056626967710244</v>
       </c>
       <c r="C63">
         <v>767.45943045334911</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-9.3856618360671362</v>
+        <v>-9.4762099347114965</v>
       </c>
       <c r="B64">
-        <v>1.0820478961181368</v>
+        <v>0.901574553364514</v>
       </c>
       <c r="C64">
         <v>767.45943045334911</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-13.632705389473941</v>
+        <v>-13.705549259536765</v>
       </c>
       <c r="B65">
-        <v>2.7603009400097194</v>
+        <v>2.6241506087873088</v>
       </c>
       <c r="C65">
         <v>767.45943045334911</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-17.878134448638853</v>
+        <v>-17.930881148931611</v>
       </c>
       <c r="B66">
-        <v>4.442673951750038</v>
+        <v>4.3567470449091816</v>
       </c>
       <c r="C66">
         <v>767.45943045334911</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-22.12206588465137</v>
+        <v>-22.152324496392286</v>
       </c>
       <c r="B67">
-        <v>6.1288686923496369</v>
+        <v>6.0990665748204176</v>
       </c>
       <c r="C67">
         <v>767.45943045334911</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-26.364431829815455</v>
+        <v>-26.369810125421111</v>
       </c>
       <c r="B68">
-        <v>7.819058350859498</v>
+        <v>7.8512821707008538</v>
       </c>
       <c r="C68">
         <v>767.45943045334911</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-30.605118231738732</v>
+        <v>-30.583221842021974</v>
       </c>
       <c r="B69">
-        <v>9.5135339733407278</v>
+        <v>9.6136843695027387</v>
       </c>
       <c r="C69">
         <v>767.45943045334911</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-34.844011038028782</v>
+        <v>-34.792443452198718</v>
       </c>
       <c r="B70">
-        <v>11.212586605854414</v>
+        <v>11.386563708178292</v>
       </c>
       <c r="C70">
         <v>767.45943045334911</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>-39.081001698988359</v>
+        <v>-38.997364348834722</v>
       </c>
       <c r="B71">
-        <v>12.916493252338443</v>
+        <v>13.170196753982559</v>
       </c>
       <c r="C71">
         <v>767.45943045334911</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>-43.31600367570077</v>
+        <v>-43.197896272331349</v>
       </c>
       <c r="B72">
-        <v>14.625474748237846</v>
+        <v>14.964804195381788</v>
       </c>
       <c r="C72">
         <v>767.45943045334911</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>-47.548935931944463</v>
+        <v>-47.393956549969445</v>
       </c>
       <c r="B73">
-        <v>16.339737886874442</v>
+        <v>16.770592751145024</v>
       </c>
       <c r="C73">
         <v>767.45943045334911</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>-51.779717431497922</v>
+        <v>-51.585462509029874</v>
       </c>
       <c r="B74">
-        <v>18.05948946157006</v>
+        <v>18.587769140041331</v>
       </c>
       <c r="C74">
         <v>767.45943045334911</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>-56.007861888341729</v>
+        <v>-55.77191902208331</v>
       </c>
       <c r="B75">
-        <v>19.785970407543385</v>
+        <v>20.417571402064691</v>
       </c>
       <c r="C75">
         <v>767.45943045334911</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>-60.231262017265145</v>
+        <v>-59.951181142859816</v>
       </c>
       <c r="B76">
-        <v>21.524558227600647</v>
+        <v>22.265362862108859</v>
       </c>
       <c r="C76">
         <v>767.45943045334911</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>-64.448841910195824</v>
+        <v>-64.122153595863026</v>
       </c>
       <c r="B77">
-        <v>23.277998491562609</v>
+        <v>24.133882198721402</v>
       </c>
       <c r="C77">
         <v>767.45943045334911</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>-68.6652721668063</v>
+        <v>-68.289589607531539</v>
       </c>
       <c r="B78">
-        <v>25.03437246972063</v>
+        <v>26.011244220165384</v>
       </c>
       <c r="C78">
         <v>767.45943045334911</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>-72.884988773492</v>
+        <v>-72.458003613092373</v>
       </c>
       <c r="B79">
-        <v>26.78236013326806</v>
+        <v>27.886160819520182</v>
       </c>
       <c r="C79">
         <v>767.45943045334911</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>-77.105742755794651</v>
+        <v>-76.625106380991227</v>
       </c>
       <c r="B80">
-        <v>28.527700556535478</v>
+        <v>29.764356099414798</v>
       </c>
       <c r="C80">
         <v>767.45943045334911</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>-81.323613899042655</v>
+        <v>-80.786907762978359</v>
       </c>
       <c r="B81">
-        <v>30.280397589637744</v>
+        <v>31.655807214865661</v>
       </c>
       <c r="C81">
         <v>767.45943045334911</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>-85.534681988564387</v>
+        <v>-84.939417610804114</v>
       </c>
       <c r="B82">
-        <v>32.050455082689751</v>
+        <v>33.57049132088919</v>
       </c>
       <c r="C82">
         <v>767.45943045334911</v>
